--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/193.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/193.xlsx
@@ -426,13 +426,13 @@
         <v>6.627029207133406</v>
       </c>
       <c r="E2">
-        <v>-14.39660512023866</v>
+        <v>-12.87204906081636</v>
       </c>
       <c r="F2">
-        <v>-3.091536048989695</v>
+        <v>-3.459586312992738</v>
       </c>
       <c r="G2">
-        <v>-7.817119500547524</v>
+        <v>-5.00622135733638</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.410597585009009</v>
       </c>
       <c r="E3">
-        <v>-14.10892928042739</v>
+        <v>-13.24724218929986</v>
       </c>
       <c r="F3">
-        <v>-3.502344981590443</v>
+        <v>-3.542600323896887</v>
       </c>
       <c r="G3">
-        <v>-7.716055166324653</v>
+        <v>-5.673547884960509</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>6.108301280638734</v>
       </c>
       <c r="E4">
-        <v>-15.15495243451115</v>
+        <v>-13.46465422640811</v>
       </c>
       <c r="F4">
-        <v>-3.332070748475393</v>
+        <v>-3.477825306467577</v>
       </c>
       <c r="G4">
-        <v>-7.182368741029824</v>
+        <v>-4.695900750121717</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.755954210144123</v>
       </c>
       <c r="E5">
-        <v>-16.61274067316436</v>
+        <v>-14.74283865744311</v>
       </c>
       <c r="F5">
-        <v>-3.472273588134015</v>
+        <v>-3.534849290108892</v>
       </c>
       <c r="G5">
-        <v>-7.132905880127573</v>
+        <v>-4.610203968292143</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.37131792940135</v>
       </c>
       <c r="E6">
-        <v>-15.77047620705573</v>
+        <v>-14.81575161744061</v>
       </c>
       <c r="F6">
-        <v>-3.781789754720439</v>
+        <v>-3.403517436966851</v>
       </c>
       <c r="G6">
-        <v>-7.020476443068384</v>
+        <v>-4.552021130439452</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.991871216669294</v>
       </c>
       <c r="E7">
-        <v>-16.70807410797384</v>
+        <v>-16.02906112984172</v>
       </c>
       <c r="F7">
-        <v>-3.966736859641276</v>
+        <v>-3.114579573400772</v>
       </c>
       <c r="G7">
-        <v>-6.977558530697272</v>
+        <v>-3.558294675916419</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.649493281864554</v>
       </c>
       <c r="E8">
-        <v>-17.76792722167702</v>
+        <v>-16.09337904617266</v>
       </c>
       <c r="F8">
-        <v>-3.703847009056228</v>
+        <v>-3.570141883305165</v>
       </c>
       <c r="G8">
-        <v>-6.480847588530563</v>
+        <v>-3.95793049123508</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.367405145153906</v>
       </c>
       <c r="E9">
-        <v>-17.81753665443105</v>
+        <v>-16.63224933918941</v>
       </c>
       <c r="F9">
-        <v>-3.79347222020212</v>
+        <v>-3.613144920286696</v>
       </c>
       <c r="G9">
-        <v>-7.57239404264798</v>
+        <v>-3.477772276764727</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.165207009069619</v>
       </c>
       <c r="E10">
-        <v>-17.71108128745874</v>
+        <v>-17.68587580113205</v>
       </c>
       <c r="F10">
-        <v>-3.55724503121098</v>
+        <v>-3.839768845977182</v>
       </c>
       <c r="G10">
-        <v>-6.254508900556131</v>
+        <v>-2.673170667809178</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.060665744381097</v>
       </c>
       <c r="E11">
-        <v>-18.70178913153881</v>
+        <v>-17.40593459492588</v>
       </c>
       <c r="F11">
-        <v>-3.918614512110445</v>
+        <v>-3.630118996737461</v>
       </c>
       <c r="G11">
-        <v>-5.080503378146547</v>
+        <v>-2.649546614840939</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.052410933649004</v>
       </c>
       <c r="E12">
-        <v>-19.42226481768515</v>
+        <v>-18.87158879293041</v>
       </c>
       <c r="F12">
-        <v>-3.663744086351898</v>
+        <v>-3.833555262088783</v>
       </c>
       <c r="G12">
-        <v>-5.46268268683663</v>
+        <v>-2.61166073168952</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.126609105217398</v>
       </c>
       <c r="E13">
-        <v>-20.1974082420521</v>
+        <v>-19.3833878683293</v>
       </c>
       <c r="F13">
-        <v>-3.513860116856759</v>
+        <v>-3.736473915950292</v>
       </c>
       <c r="G13">
-        <v>-3.701310243212935</v>
+        <v>-1.709722462788321</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.275392131670364</v>
       </c>
       <c r="E14">
-        <v>-21.470815133009</v>
+        <v>-19.64034254047253</v>
       </c>
       <c r="F14">
-        <v>-4.10608813760982</v>
+        <v>-3.644829973443777</v>
       </c>
       <c r="G14">
-        <v>-4.284502566502026</v>
+        <v>-2.163767094044903</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.47714283197965</v>
       </c>
       <c r="E15">
-        <v>-22.17169611212416</v>
+        <v>-20.04967583449987</v>
       </c>
       <c r="F15">
-        <v>-3.791764126617548</v>
+        <v>-3.946869295852533</v>
       </c>
       <c r="G15">
-        <v>-4.349068136154432</v>
+        <v>-1.034649258602297</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.703736366512501</v>
       </c>
       <c r="E16">
-        <v>-22.32869377749608</v>
+        <v>-21.59394886975156</v>
       </c>
       <c r="F16">
-        <v>-3.165042887211915</v>
+        <v>-3.45410997609283</v>
       </c>
       <c r="G16">
-        <v>-3.281413889193935</v>
+        <v>0.1055224883959352</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.93983492735944</v>
       </c>
       <c r="E17">
-        <v>-22.80351333414833</v>
+        <v>-21.77079483669911</v>
       </c>
       <c r="F17">
-        <v>-3.616666310115997</v>
+        <v>-3.472238796703098</v>
       </c>
       <c r="G17">
-        <v>-2.86621519929516</v>
+        <v>-0.06834074223550902</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.165735379564194</v>
       </c>
       <c r="E18">
-        <v>-23.89981613513925</v>
+        <v>-23.92172942086237</v>
       </c>
       <c r="F18">
-        <v>-3.116930480089917</v>
+        <v>-3.42851176661152</v>
       </c>
       <c r="G18">
-        <v>-2.056773572761198</v>
+        <v>0.1355127204361929</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.357216897280656</v>
       </c>
       <c r="E19">
-        <v>-24.23408544401544</v>
+        <v>-22.51248642357139</v>
       </c>
       <c r="F19">
-        <v>-3.051716427937123</v>
+        <v>-3.409317665521252</v>
       </c>
       <c r="G19">
-        <v>-3.00475821956812</v>
+        <v>0.02225233644664701</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.49992493740413</v>
       </c>
       <c r="E20">
-        <v>-25.81555989324016</v>
+        <v>-24.22974716591609</v>
       </c>
       <c r="F20">
-        <v>-3.128924411715051</v>
+        <v>-2.932935169314896</v>
       </c>
       <c r="G20">
-        <v>-2.174595888503859</v>
+        <v>0.7398230137202946</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.580531234996331</v>
       </c>
       <c r="E21">
-        <v>-25.22212148843099</v>
+        <v>-24.60963632194555</v>
       </c>
       <c r="F21">
-        <v>-2.529900464789422</v>
+        <v>-2.948430609951664</v>
       </c>
       <c r="G21">
-        <v>-1.919640844887967</v>
+        <v>0.369290204237367</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.584535027717783</v>
       </c>
       <c r="E22">
-        <v>-25.09978929158778</v>
+        <v>-25.64007699696892</v>
       </c>
       <c r="F22">
-        <v>-2.462555023309225</v>
+        <v>-2.680204416557781</v>
       </c>
       <c r="G22">
-        <v>-2.075696651063672</v>
+        <v>0.67952142672247</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.50411852817467</v>
       </c>
       <c r="E23">
-        <v>-25.91475611637818</v>
+        <v>-25.22813983038718</v>
       </c>
       <c r="F23">
-        <v>-2.657628919729286</v>
+        <v>-2.522378888772002</v>
       </c>
       <c r="G23">
-        <v>-2.526639301149957</v>
+        <v>1.509058064679808</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.340175893806117</v>
       </c>
       <c r="E24">
-        <v>-26.82389708663208</v>
+        <v>-25.17796433838219</v>
       </c>
       <c r="F24">
-        <v>-2.130927245639874</v>
+        <v>-2.469458637244156</v>
       </c>
       <c r="G24">
-        <v>-1.079967316489381</v>
+        <v>0.9590175444209792</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.094782310586577</v>
       </c>
       <c r="E25">
-        <v>-27.98241659201439</v>
+        <v>-26.78735230139018</v>
       </c>
       <c r="F25">
-        <v>-2.495396477360614</v>
+        <v>-2.552949787772318</v>
       </c>
       <c r="G25">
-        <v>-2.515184813584079</v>
+        <v>0.8017269047591266</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.772945817143645</v>
       </c>
       <c r="E26">
-        <v>-28.86970314670728</v>
+        <v>-26.56311585395237</v>
       </c>
       <c r="F26">
-        <v>-2.294534777897193</v>
+        <v>-2.654328703996533</v>
       </c>
       <c r="G26">
-        <v>-1.592860205252048</v>
+        <v>-0.2853867288812066</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.391006499308532</v>
       </c>
       <c r="E27">
-        <v>-26.70822174658015</v>
+        <v>-26.32658459958373</v>
       </c>
       <c r="F27">
-        <v>-2.518857498942702</v>
+        <v>-2.388204078703553</v>
       </c>
       <c r="G27">
-        <v>-3.463066833479284</v>
+        <v>0.5289743683241127</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.963888704107513</v>
       </c>
       <c r="E28">
-        <v>-26.58614767275538</v>
+        <v>-25.05895151298661</v>
       </c>
       <c r="F28">
-        <v>-2.180249897537362</v>
+        <v>-2.840292215720605</v>
       </c>
       <c r="G28">
-        <v>-2.396223670175908</v>
+        <v>-0.1822433720596735</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.506349087045324</v>
       </c>
       <c r="E29">
-        <v>-26.55494648684253</v>
+        <v>-25.40412085879926</v>
       </c>
       <c r="F29">
-        <v>-2.328294063030884</v>
+        <v>-2.403572779127692</v>
       </c>
       <c r="G29">
-        <v>-2.401004097934616</v>
+        <v>0.0810012775865535</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.041290851612473</v>
       </c>
       <c r="E30">
-        <v>-28.08680697483921</v>
+        <v>-24.84154853282637</v>
       </c>
       <c r="F30">
-        <v>-1.840963863229129</v>
+        <v>-2.630160256652454</v>
       </c>
       <c r="G30">
-        <v>-2.651102571244397</v>
+        <v>-0.8835162336434891</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.589199207144222</v>
       </c>
       <c r="E31">
-        <v>-26.42158292731664</v>
+        <v>-24.66746040654949</v>
       </c>
       <c r="F31">
-        <v>-1.686755815891376</v>
+        <v>-2.334546580187214</v>
       </c>
       <c r="G31">
-        <v>-2.959691763142021</v>
+        <v>-0.9573380886236973</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.165666864346037</v>
       </c>
       <c r="E32">
-        <v>-27.51315800144356</v>
+        <v>-24.89266594742495</v>
       </c>
       <c r="F32">
-        <v>-2.132711549025504</v>
+        <v>-2.089539525093802</v>
       </c>
       <c r="G32">
-        <v>-2.793131595970209</v>
+        <v>0.0002670035203470524</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.788920898593713</v>
       </c>
       <c r="E33">
-        <v>-24.93474452790423</v>
+        <v>-24.79723741466131</v>
       </c>
       <c r="F33">
-        <v>-2.012156755793883</v>
+        <v>-2.339285670098631</v>
       </c>
       <c r="G33">
-        <v>-2.129082508429959</v>
+        <v>-0.9142745122488577</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.474588726515426</v>
       </c>
       <c r="E34">
-        <v>-25.00553363359213</v>
+        <v>-24.10955693727852</v>
       </c>
       <c r="F34">
-        <v>-2.059553453479863</v>
+        <v>-2.406013977863742</v>
       </c>
       <c r="G34">
-        <v>-2.651777922534408</v>
+        <v>-0.8604715261446223</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.229398899369646</v>
       </c>
       <c r="E35">
-        <v>-25.88240469806738</v>
+        <v>-23.55137270261906</v>
       </c>
       <c r="F35">
-        <v>-1.716545564430852</v>
+        <v>-2.303313815632062</v>
       </c>
       <c r="G35">
-        <v>-3.282804318320428</v>
+        <v>-0.5558516783485841</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.056766668439618</v>
       </c>
       <c r="E36">
-        <v>-24.90640986603823</v>
+        <v>-23.28093223488099</v>
       </c>
       <c r="F36">
-        <v>-1.753275375070982</v>
+        <v>-2.315929851176698</v>
       </c>
       <c r="G36">
-        <v>-2.425316744375023</v>
+        <v>-0.9144863871633711</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9607131368689368</v>
       </c>
       <c r="E37">
-        <v>-24.47572934553874</v>
+        <v>-23.2588559240936</v>
       </c>
       <c r="F37">
-        <v>-1.768286220777112</v>
+        <v>-2.100000148656354</v>
       </c>
       <c r="G37">
-        <v>-3.71250650822675</v>
+        <v>-1.114800876653592</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9358438601113426</v>
       </c>
       <c r="E38">
-        <v>-24.28783390201248</v>
+        <v>-22.21506077922161</v>
       </c>
       <c r="F38">
-        <v>-1.287825671846773</v>
+        <v>-1.908860169032188</v>
       </c>
       <c r="G38">
-        <v>-2.827826113221771</v>
+        <v>-1.054290725286793</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.9711670824218144</v>
       </c>
       <c r="E39">
-        <v>-22.97682709136989</v>
+        <v>-21.72632069346978</v>
       </c>
       <c r="F39">
-        <v>-1.878572571683629</v>
+        <v>-1.746815766063951</v>
       </c>
       <c r="G39">
-        <v>-3.366743200468649</v>
+        <v>-0.1705174197595749</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.059753923371354</v>
       </c>
       <c r="E40">
-        <v>-22.97111668564622</v>
+        <v>-21.80924158102423</v>
       </c>
       <c r="F40">
-        <v>-2.125623209159748</v>
+        <v>-2.091521808288701</v>
       </c>
       <c r="G40">
-        <v>-3.410362948494086</v>
+        <v>-0.8163088486507447</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.188273735165247</v>
       </c>
       <c r="E41">
-        <v>-21.1363601566985</v>
+        <v>-20.36184166174461</v>
       </c>
       <c r="F41">
-        <v>-1.471782877721265</v>
+        <v>-1.849609533812147</v>
       </c>
       <c r="G41">
-        <v>-3.215100351496794</v>
+        <v>-0.6712606063931169</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.340417344818354</v>
       </c>
       <c r="E42">
-        <v>-23.19185715115011</v>
+        <v>-18.84251598980117</v>
       </c>
       <c r="F42">
-        <v>-2.196093252483305</v>
+        <v>-2.035427252873327</v>
       </c>
       <c r="G42">
-        <v>-3.029315846378434</v>
+        <v>-0.8234794902888061</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.504672393196255</v>
       </c>
       <c r="E43">
-        <v>-21.9182102510708</v>
+        <v>-20.3773018720068</v>
       </c>
       <c r="F43">
-        <v>-1.857542808428758</v>
+        <v>-1.882137036617876</v>
       </c>
       <c r="G43">
-        <v>-3.506170136400595</v>
+        <v>-1.105898819698492</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.667396710010051</v>
       </c>
       <c r="E44">
-        <v>-21.2111026201951</v>
+        <v>-19.47479964464814</v>
       </c>
       <c r="F44">
-        <v>-1.643409006437683</v>
+        <v>-1.672140101436381</v>
       </c>
       <c r="G44">
-        <v>-3.429464796255681</v>
+        <v>-0.2465871351609483</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.813701438321405</v>
       </c>
       <c r="E45">
-        <v>-19.84577223535649</v>
+        <v>-18.55613076508209</v>
       </c>
       <c r="F45">
-        <v>-1.628949025054415</v>
+        <v>-1.847491398363189</v>
       </c>
       <c r="G45">
-        <v>-2.682880497875861</v>
+        <v>-1.311457213322918</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.932021386334323</v>
       </c>
       <c r="E46">
-        <v>-19.31816425719683</v>
+        <v>-17.55642937162279</v>
       </c>
       <c r="F46">
-        <v>-1.529060341787837</v>
+        <v>-1.927774281940309</v>
       </c>
       <c r="G46">
-        <v>-3.000583621643099</v>
+        <v>-0.5435397594880345</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.012128210796604</v>
       </c>
       <c r="E47">
-        <v>-17.74004087873779</v>
+        <v>-17.80991070420214</v>
       </c>
       <c r="F47">
-        <v>-1.614360646723713</v>
+        <v>-2.064589098921481</v>
       </c>
       <c r="G47">
-        <v>-3.330509279541326</v>
+        <v>-1.44622290113557</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.044976065279396</v>
       </c>
       <c r="E48">
-        <v>-17.06681981886148</v>
+        <v>-17.69471991086903</v>
       </c>
       <c r="F48">
-        <v>-1.166746522049181</v>
+        <v>-2.033125219860947</v>
       </c>
       <c r="G48">
-        <v>-3.566905404864064</v>
+        <v>-0.8848603151324331</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.024942315404736</v>
       </c>
       <c r="E49">
-        <v>-18.50090602455855</v>
+        <v>-17.06616319013037</v>
       </c>
       <c r="F49">
-        <v>-1.357962711474404</v>
+        <v>-1.716818925673776</v>
       </c>
       <c r="G49">
-        <v>-3.304657229425158</v>
+        <v>-0.7630984501980389</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.95055221049581</v>
       </c>
       <c r="E50">
-        <v>-15.12313990460727</v>
+        <v>-15.27915489111953</v>
       </c>
       <c r="F50">
-        <v>-1.095270012331222</v>
+        <v>-1.634854456268973</v>
       </c>
       <c r="G50">
-        <v>-4.199838674880704</v>
+        <v>-0.9958430437909604</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.822918179488067</v>
       </c>
       <c r="E51">
-        <v>-17.35093627810272</v>
+        <v>-15.82557867878106</v>
       </c>
       <c r="F51">
-        <v>-1.960243799027841</v>
+        <v>-1.998453073849371</v>
       </c>
       <c r="G51">
-        <v>-4.368914856662363</v>
+        <v>-1.929009688764105</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.645938975112256</v>
       </c>
       <c r="E52">
-        <v>-15.91548700172935</v>
+        <v>-14.74425606980751</v>
       </c>
       <c r="F52">
-        <v>-1.539008205928056</v>
+        <v>-1.738793856135241</v>
       </c>
       <c r="G52">
-        <v>-3.888822853102794</v>
+        <v>-1.235430535013555</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.426503099208758</v>
       </c>
       <c r="E53">
-        <v>-14.85541199279979</v>
+        <v>-13.626941149421</v>
       </c>
       <c r="F53">
-        <v>-1.262979619967205</v>
+        <v>-1.822635406074787</v>
       </c>
       <c r="G53">
-        <v>-3.796968456570176</v>
+        <v>-1.037694960498427</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.172442828794501</v>
       </c>
       <c r="E54">
-        <v>-15.49452458645032</v>
+        <v>-13.88489661431992</v>
       </c>
       <c r="F54">
-        <v>-1.349944115015305</v>
+        <v>-1.856331735285865</v>
       </c>
       <c r="G54">
-        <v>-4.857336192798737</v>
+        <v>-1.25512497042668</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8931433223133912</v>
       </c>
       <c r="E55">
-        <v>-14.84481083514783</v>
+        <v>-14.38901992627581</v>
       </c>
       <c r="F55">
-        <v>-1.432292946895007</v>
+        <v>-1.628452004612736</v>
       </c>
       <c r="G55">
-        <v>-4.138070516208982</v>
+        <v>-2.34870409950521</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.5984677010231948</v>
       </c>
       <c r="E56">
-        <v>-14.91382930749874</v>
+        <v>-13.4001732850129</v>
       </c>
       <c r="F56">
-        <v>-1.549120915181432</v>
+        <v>-2.067374070129693</v>
       </c>
       <c r="G56">
-        <v>-4.977465958782271</v>
+        <v>-1.880467159521771</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.2982003009995099</v>
       </c>
       <c r="E57">
-        <v>-14.25853194774479</v>
+        <v>-12.7406553874838</v>
       </c>
       <c r="F57">
-        <v>-1.460641336153612</v>
+        <v>-1.81301971726309</v>
       </c>
       <c r="G57">
-        <v>-4.910245331607369</v>
+        <v>-2.545280983081593</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.001988224663199663</v>
       </c>
       <c r="E58">
-        <v>-13.21220538590251</v>
+        <v>-13.14163817544099</v>
       </c>
       <c r="F58">
-        <v>-1.691966246854985</v>
+        <v>-1.767437972556645</v>
       </c>
       <c r="G58">
-        <v>-4.294288539116112</v>
+        <v>-1.918147788849756</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.2825399652254794</v>
       </c>
       <c r="E59">
-        <v>-13.20875921718268</v>
+        <v>-11.47289097514045</v>
       </c>
       <c r="F59">
-        <v>-1.615607339664926</v>
+        <v>-1.706490012528268</v>
       </c>
       <c r="G59">
-        <v>-4.653605220311988</v>
+        <v>-2.206939918422539</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.5492046377318464</v>
       </c>
       <c r="E60">
-        <v>-12.60707446120554</v>
+        <v>-13.26178311933849</v>
       </c>
       <c r="F60">
-        <v>-1.423697806723559</v>
+        <v>-1.94397217813465</v>
       </c>
       <c r="G60">
-        <v>-5.121448205376253</v>
+        <v>-2.093053841326071</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.7943875389573455</v>
       </c>
       <c r="E61">
-        <v>-13.49917931224259</v>
+        <v>-11.94661464108285</v>
       </c>
       <c r="F61">
-        <v>-1.358198796184202</v>
+        <v>-1.723382908973559</v>
       </c>
       <c r="G61">
-        <v>-4.338285689333025</v>
+        <v>-2.776532520636303</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.0173831578788</v>
       </c>
       <c r="E62">
-        <v>-13.14209102284175</v>
+        <v>-11.70763348227606</v>
       </c>
       <c r="F62">
-        <v>-1.106749527799218</v>
+        <v>-1.910429925260493</v>
       </c>
       <c r="G62">
-        <v>-5.127854110994742</v>
+        <v>-2.631298887828477</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.219153767297288</v>
       </c>
       <c r="E63">
-        <v>-13.59225303852224</v>
+        <v>-10.74084956637852</v>
       </c>
       <c r="F63">
-        <v>-1.220347691582128</v>
+        <v>-1.492008296228018</v>
       </c>
       <c r="G63">
-        <v>-5.100072012829179</v>
+        <v>-2.404649008573353</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.402282563493579</v>
       </c>
       <c r="E64">
-        <v>-12.54786919202926</v>
+        <v>-10.86948992751441</v>
       </c>
       <c r="F64">
-        <v>-1.243708480708477</v>
+        <v>-1.843010759081447</v>
       </c>
       <c r="G64">
-        <v>-4.399524160718464</v>
+        <v>-2.503760120928054</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.569083166838724</v>
       </c>
       <c r="E65">
-        <v>-12.19495615566349</v>
+        <v>-11.08272218311358</v>
       </c>
       <c r="F65">
-        <v>-1.709443970686652</v>
+        <v>-1.529131581384477</v>
       </c>
       <c r="G65">
-        <v>-5.666589118236961</v>
+        <v>-2.517598201282208</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.723161738099362</v>
       </c>
       <c r="E66">
-        <v>-12.86580882363378</v>
+        <v>-10.96837821441991</v>
       </c>
       <c r="F66">
-        <v>-1.939320066800528</v>
+        <v>-1.716376577480681</v>
       </c>
       <c r="G66">
-        <v>-5.488650606046674</v>
+        <v>-2.441495380425442</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.867842183842789</v>
       </c>
       <c r="E67">
-        <v>-12.32542149182447</v>
+        <v>-10.78547767772411</v>
       </c>
       <c r="F67">
-        <v>-1.489213384610972</v>
+        <v>-2.063707716004902</v>
       </c>
       <c r="G67">
-        <v>-5.153570428743802</v>
+        <v>-2.421357331910055</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.003584325212944</v>
       </c>
       <c r="E68">
-        <v>-12.36486902890529</v>
+        <v>-10.41963131959244</v>
       </c>
       <c r="F68">
-        <v>-1.606127503107289</v>
+        <v>-2.171991902898853</v>
       </c>
       <c r="G68">
-        <v>-5.429378598711563</v>
+        <v>-2.536604043223164</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.133582286171736</v>
       </c>
       <c r="E69">
-        <v>-11.76274953942342</v>
+        <v>-10.59551725005035</v>
       </c>
       <c r="F69">
-        <v>-1.872153552679336</v>
+        <v>-1.683700796909851</v>
       </c>
       <c r="G69">
-        <v>-5.330982564193344</v>
+        <v>-2.248176073659701</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.258998077367473</v>
       </c>
       <c r="E70">
-        <v>-11.39533180081108</v>
+        <v>-11.94533308293868</v>
       </c>
       <c r="F70">
-        <v>-1.770169928251078</v>
+        <v>-2.013015772790586</v>
       </c>
       <c r="G70">
-        <v>-5.675802366472753</v>
+        <v>-2.81670268020982</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.377376700354347</v>
       </c>
       <c r="E71">
-        <v>-12.72468345965875</v>
+        <v>-10.83605620391578</v>
       </c>
       <c r="F71">
-        <v>-2.217474243516963</v>
+        <v>-1.927612750296763</v>
       </c>
       <c r="G71">
-        <v>-5.52800306087199</v>
+        <v>-2.491305848609316</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.487106604988078</v>
       </c>
       <c r="E72">
-        <v>-13.39090349871919</v>
+        <v>-10.14304118415195</v>
       </c>
       <c r="F72">
-        <v>-2.101934386541891</v>
+        <v>-2.367749202426224</v>
       </c>
       <c r="G72">
-        <v>-4.020718297932897</v>
+        <v>-2.519501764967289</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.585821466755024</v>
       </c>
       <c r="E73">
-        <v>-10.83367875506175</v>
+        <v>-10.75508256018462</v>
       </c>
       <c r="F73">
-        <v>-2.147709140853189</v>
+        <v>-2.584430234180908</v>
       </c>
       <c r="G73">
-        <v>-4.48707153750449</v>
+        <v>-2.361837033659498</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.668305710081807</v>
       </c>
       <c r="E74">
-        <v>-12.80162223304907</v>
+        <v>-11.69834105361232</v>
       </c>
       <c r="F74">
-        <v>-2.400867331190149</v>
+        <v>-2.765785538043206</v>
       </c>
       <c r="G74">
-        <v>-5.14467168233424</v>
+        <v>-2.467191834901265</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.729074419324435</v>
       </c>
       <c r="E75">
-        <v>-13.15798596660868</v>
+        <v>-11.45386685583423</v>
       </c>
       <c r="F75">
-        <v>-2.481440143358248</v>
+        <v>-2.318449744816014</v>
       </c>
       <c r="G75">
-        <v>-4.697976462174839</v>
+        <v>-2.168716359626114</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.765540353996413</v>
       </c>
       <c r="E76">
-        <v>-13.32952909049324</v>
+        <v>-11.93582328752257</v>
       </c>
       <c r="F76">
-        <v>-2.330729463195115</v>
+        <v>-2.851815634660949</v>
       </c>
       <c r="G76">
-        <v>-5.500409663802165</v>
+        <v>-2.324987351261871</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.773281980260029</v>
       </c>
       <c r="E77">
-        <v>-14.80443496089544</v>
+        <v>-12.24723285960804</v>
       </c>
       <c r="F77">
-        <v>-2.757621148921214</v>
+        <v>-2.984337851760814</v>
       </c>
       <c r="G77">
-        <v>-3.586331686088507</v>
+        <v>-2.516343504522824</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.747410191702818</v>
       </c>
       <c r="E78">
-        <v>-13.73590529099356</v>
+        <v>-13.19512851041959</v>
       </c>
       <c r="F78">
-        <v>-1.910735592832126</v>
+        <v>-3.014930288313602</v>
       </c>
       <c r="G78">
-        <v>-4.588010070996869</v>
+        <v>-1.96296264381487</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.688139400206566</v>
       </c>
       <c r="E79">
-        <v>-15.16890466292878</v>
+        <v>-13.57733624514097</v>
       </c>
       <c r="F79">
-        <v>-2.758219230186036</v>
+        <v>-3.196106664816896</v>
       </c>
       <c r="G79">
-        <v>-3.647381456378207</v>
+        <v>-1.365455521613971</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.595323837639937</v>
       </c>
       <c r="E80">
-        <v>-15.23247085257445</v>
+        <v>-13.56924839056328</v>
       </c>
       <c r="F80">
-        <v>-2.821405438936776</v>
+        <v>-3.205134212772605</v>
       </c>
       <c r="G80">
-        <v>-4.035390635762948</v>
+        <v>-1.940447623602287</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.46881518156202</v>
       </c>
       <c r="E81">
-        <v>-16.02257635506274</v>
+        <v>-14.09036253699594</v>
       </c>
       <c r="F81">
-        <v>-2.459806500266736</v>
+        <v>-3.102222816853212</v>
       </c>
       <c r="G81">
-        <v>-3.387218924629042</v>
+        <v>-1.486191117431191</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.313018375977619</v>
       </c>
       <c r="E82">
-        <v>-16.71368035879533</v>
+        <v>-14.27088109636371</v>
       </c>
       <c r="F82">
-        <v>-2.527114665213807</v>
+        <v>-3.096626366679898</v>
       </c>
       <c r="G82">
-        <v>-4.178714083794615</v>
+        <v>-0.8124951001895042</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.132963820881256</v>
       </c>
       <c r="E83">
-        <v>-17.35478095253523</v>
+        <v>-16.25291265698888</v>
       </c>
       <c r="F83">
-        <v>-2.93749616023471</v>
+        <v>-3.427194662441069</v>
       </c>
       <c r="G83">
-        <v>-4.146876567343444</v>
+        <v>-0.8301601711870553</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.932930745677378</v>
       </c>
       <c r="E84">
-        <v>-18.95359945720932</v>
+        <v>-17.18351406556514</v>
       </c>
       <c r="F84">
-        <v>-3.221005732210244</v>
+        <v>-3.657733452477185</v>
       </c>
       <c r="G84">
-        <v>-3.465735133183936</v>
+        <v>-0.7455922853863729</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.719257818736197</v>
       </c>
       <c r="E85">
-        <v>-18.7101079382909</v>
+        <v>-17.63453649130708</v>
       </c>
       <c r="F85">
-        <v>-3.248124824243094</v>
+        <v>-3.6119330187764</v>
       </c>
       <c r="G85">
-        <v>-3.401642971543646</v>
+        <v>-0.2359040047057201</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.500568257408723</v>
       </c>
       <c r="E86">
-        <v>-20.11166158671686</v>
+        <v>-19.42184819807645</v>
       </c>
       <c r="F86">
-        <v>-3.436124463043247</v>
+        <v>-3.902693290628638</v>
       </c>
       <c r="G86">
-        <v>-3.804053024024216</v>
+        <v>-0.6701283998186861</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.283992910975148</v>
       </c>
       <c r="E87">
-        <v>-21.31585075246652</v>
+        <v>-20.73337125475591</v>
       </c>
       <c r="F87">
-        <v>-3.659509472188787</v>
+        <v>-4.218711312959636</v>
       </c>
       <c r="G87">
-        <v>-2.986868031473898</v>
+        <v>-0.5178168206478974</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.076720351439028</v>
       </c>
       <c r="E88">
-        <v>-23.50544944770727</v>
+        <v>-21.8183166429356</v>
       </c>
       <c r="F88">
-        <v>-3.462038280505024</v>
+        <v>-3.69287859627576</v>
       </c>
       <c r="G88">
-        <v>-3.919256698245314</v>
+        <v>-0.08623755142080906</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8904748971880826</v>
       </c>
       <c r="E89">
-        <v>-23.27803401151608</v>
+        <v>-22.6091376443171</v>
       </c>
       <c r="F89">
-        <v>-3.296079013191157</v>
+        <v>-4.021323786383555</v>
       </c>
       <c r="G89">
-        <v>-2.531452834364058</v>
+        <v>-0.8386020623121968</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.7339851783043088</v>
       </c>
       <c r="E90">
-        <v>-24.94351165358307</v>
+        <v>-25.0944275783627</v>
       </c>
       <c r="F90">
-        <v>-3.197335133675248</v>
+        <v>-4.501486951416289</v>
       </c>
       <c r="G90">
-        <v>-3.654701072565536</v>
+        <v>-0.4617096948483293</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6134480739486179</v>
       </c>
       <c r="E91">
-        <v>-25.08921077630586</v>
+        <v>-25.27159959543879</v>
       </c>
       <c r="F91">
-        <v>-3.235407727875316</v>
+        <v>-4.344849302486125</v>
       </c>
       <c r="G91">
-        <v>-2.966379065131349</v>
+        <v>-1.066450359052536</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.5386009879005538</v>
       </c>
       <c r="E92">
-        <v>-27.82903717737459</v>
+        <v>-26.55686655982178</v>
       </c>
       <c r="F92">
-        <v>-4.020936110439045</v>
+        <v>-4.759714750258381</v>
       </c>
       <c r="G92">
-        <v>-4.070297027929023</v>
+        <v>-1.112950281697139</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5148501327423719</v>
       </c>
       <c r="E93">
-        <v>-29.78430092814043</v>
+        <v>-29.59059771669934</v>
       </c>
       <c r="F93">
-        <v>-4.135822385533308</v>
+        <v>-4.993533875209584</v>
       </c>
       <c r="G93">
-        <v>-2.815063960167881</v>
+        <v>-1.537584026382837</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5419050102582466</v>
       </c>
       <c r="E94">
-        <v>-31.64757778638846</v>
+        <v>-30.7994512106769</v>
       </c>
       <c r="F94">
-        <v>-4.385865086068339</v>
+        <v>-4.718322059507893</v>
       </c>
       <c r="G94">
-        <v>-3.892944482299187</v>
+        <v>-1.058541465759217</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.6207825744071153</v>
       </c>
       <c r="E95">
-        <v>-33.46936703001522</v>
+        <v>-33.43287885069842</v>
       </c>
       <c r="F95">
-        <v>-4.421411159689869</v>
+        <v>-4.993900013601621</v>
       </c>
       <c r="G95">
-        <v>-4.174135599313803</v>
+        <v>-1.542761719606257</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.7501888254631194</v>
       </c>
       <c r="E96">
-        <v>-35.86229420820037</v>
+        <v>-34.75669671430871</v>
       </c>
       <c r="F96">
-        <v>-4.333391324570602</v>
+        <v>-5.443001057764179</v>
       </c>
       <c r="G96">
-        <v>-4.260302478609954</v>
+        <v>-1.805655451425321</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.9203108824198757</v>
       </c>
       <c r="E97">
-        <v>-38.07508321883441</v>
+        <v>-37.10649470604481</v>
       </c>
       <c r="F97">
-        <v>-4.381073809010547</v>
+        <v>-5.391580979602803</v>
       </c>
       <c r="G97">
-        <v>-4.916081823393104</v>
+        <v>-1.927457042906187</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.127131590243693</v>
       </c>
       <c r="E98">
-        <v>-40.2425037126226</v>
+        <v>-38.31073142077155</v>
       </c>
       <c r="F98">
-        <v>-4.856332210651304</v>
+        <v>-5.4219986306336</v>
       </c>
       <c r="G98">
-        <v>-5.591638367227861</v>
+        <v>-2.800510801977245</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.357860543186306</v>
       </c>
       <c r="E99">
-        <v>-42.57291077865786</v>
+        <v>-41.04551536603275</v>
       </c>
       <c r="F99">
-        <v>-5.050521410685175</v>
+        <v>-5.414153162961686</v>
       </c>
       <c r="G99">
-        <v>-5.56452499926123</v>
+        <v>-2.458154045579054</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.611482448499084</v>
       </c>
       <c r="E100">
-        <v>-43.63354958260138</v>
+        <v>-43.92241188260265</v>
       </c>
       <c r="F100">
-        <v>-4.878368440300577</v>
+        <v>-6.073182387811306</v>
       </c>
       <c r="G100">
-        <v>-5.886843023510212</v>
+        <v>-3.803198903275084</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.865450385237515</v>
       </c>
       <c r="E101">
-        <v>-45.71283012254128</v>
+        <v>-44.94542812449044</v>
       </c>
       <c r="F101">
-        <v>-5.061715139399205</v>
+        <v>-5.89804480967442</v>
       </c>
       <c r="G101">
-        <v>-5.980084538623785</v>
+        <v>-3.899072302092378</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.139330982857725</v>
       </c>
       <c r="E102">
-        <v>-46.40981887824684</v>
+        <v>-46.88428521392649</v>
       </c>
       <c r="F102">
-        <v>-5.657874591845954</v>
+        <v>-5.915746192704843</v>
       </c>
       <c r="G102">
-        <v>-6.65106259797773</v>
+        <v>-3.685952622456256</v>
       </c>
     </row>
   </sheetData>
